--- a/templates/plantilla_form4.xlsx
+++ b/templates/plantilla_form4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Marcela\MONITORIA\extension-server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726042DA-5B5E-45A8-8146-4BEBA9B83FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78957014-754C-44F9-9EB4-2F519B9C57A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,9 +504,6 @@
     <t>{{boletin}}</t>
   </si>
   <si>
-    <t>{{ otro_canal}}</t>
-  </si>
-  <si>
     <t>{{nombre_dependencia}}</t>
   </si>
   <si>
@@ -518,12 +515,15 @@
   <si>
     <t>{{valorEconomico_no}}</t>
   </si>
+  <si>
+    <t>{{otro_canal}}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -593,6 +593,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -827,7 +834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -885,42 +892,63 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -938,42 +966,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1581,9 +1591,9 @@
       <c r="Y4" s="1"/>
     </row>
     <row r="5" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1635,19 +1645,19 @@
       <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:25" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -1664,17 +1674,17 @@
       <c r="Y7" s="1"/>
     </row>
     <row r="8" spans="1:25" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
+      <c r="A8" s="46"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1691,17 +1701,17 @@
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="1:25" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -1718,20 +1728,20 @@
       <c r="Y9" s="1"/>
     </row>
     <row r="10" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="40" t="s">
-        <v>136</v>
+      <c r="B10" s="46"/>
+      <c r="C10" s="49" t="s">
+        <v>135</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
       <c r="K10" s="3"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1749,20 +1759,20 @@
       <c r="Y10" s="1"/>
     </row>
     <row r="11" spans="1:25" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="41" t="s">
-        <v>137</v>
+      <c r="B11" s="46"/>
+      <c r="C11" s="50" t="s">
+        <v>136</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
       <c r="K11" s="4"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1813,7 +1823,7 @@
       <c r="B13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="27" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="42"/>
@@ -1846,17 +1856,17 @@
       <c r="B14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="32"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="52"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -1879,17 +1889,17 @@
       <c r="B15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="32"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="52"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1906,25 +1916,25 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23">
+      <c r="A16" s="32">
         <v>3</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="29" t="s">
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="27"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="26"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1941,8 +1951,8 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="9" t="s">
         <v>13</v>
       </c>
@@ -1972,25 +1982,25 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
+      <c r="A18" s="32">
         <v>4</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="35" t="s">
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="27"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="26"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -2007,21 +2017,21 @@
       <c r="Y18" s="1"/>
     </row>
     <row r="19" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
+      <c r="A19" s="55"/>
       <c r="B19" s="44"/>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="25" t="s">
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="27"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="26"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -2044,17 +2054,17 @@
       <c r="B20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="27"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="26"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -2077,17 +2087,17 @@
       <c r="B21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="27"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="26"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -2104,27 +2114,27 @@
       <c r="Y21" s="1"/>
     </row>
     <row r="22" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23">
+      <c r="A22" s="32">
         <v>7</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="29" t="s">
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="26"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="35" t="s">
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J22" s="26"/>
-      <c r="K22" s="27"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="26"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -2141,23 +2151,23 @@
       <c r="Y22" s="1"/>
     </row>
     <row r="23" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="25" t="s">
+      <c r="A23" s="33"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="25" t="s">
+      <c r="D23" s="25"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="26"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="25" t="s">
+      <c r="G23" s="25"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="27"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="26"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2174,29 +2184,29 @@
       <c r="Y23" s="1"/>
     </row>
     <row r="24" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23">
+      <c r="A24" s="32">
         <v>8</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="22" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="29" t="s">
+      <c r="E24" s="26"/>
+      <c r="F24" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="35" t="s">
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="27"/>
+      <c r="K24" s="26"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -2213,25 +2223,25 @@
       <c r="Y24" s="1"/>
     </row>
     <row r="25" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="22"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="23"/>
       <c r="C25" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="27"/>
-      <c r="F25" s="25" t="s">
+      <c r="E25" s="26"/>
+      <c r="F25" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="25" t="s">
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="K25" s="27"/>
+      <c r="K25" s="26"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -2248,10 +2258,10 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23">
+      <c r="A26" s="32">
         <v>9</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="22" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -2263,16 +2273,16 @@
       <c r="E26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="G26" s="26"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="35" t="s">
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J26" s="26"/>
-      <c r="K26" s="27"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="26"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -2289,8 +2299,8 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="22"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="8" t="s">
         <v>44</v>
       </c>
@@ -2300,16 +2310,16 @@
       <c r="E27" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="G27" s="26"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="25" t="s">
+      <c r="G27" s="25"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="J27" s="26"/>
-      <c r="K27" s="27"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="26"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -2326,27 +2336,27 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23">
+      <c r="A28" s="32">
         <v>10</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="35" t="s">
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="G28" s="26"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="35" t="s">
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J28" s="26"/>
-      <c r="K28" s="27"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="26"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -2363,23 +2373,23 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="29" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="25" t="s">
+      <c r="A29" s="33"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="25" t="s">
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="26"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="25" t="s">
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="26"/>
-      <c r="K29" s="27"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="26"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -2396,29 +2406,29 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23">
+      <c r="A30" s="32">
         <v>11</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="35" t="s">
+      <c r="D30" s="26"/>
+      <c r="E30" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="27"/>
-      <c r="G30" s="35" t="s">
+      <c r="F30" s="26"/>
+      <c r="G30" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="H30" s="27"/>
-      <c r="I30" s="35" t="s">
+      <c r="H30" s="26"/>
+      <c r="I30" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J30" s="26"/>
-      <c r="K30" s="27"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="26"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -2435,25 +2445,25 @@
       <c r="Y30" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="25" t="s">
+      <c r="A31" s="33"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="25" t="s">
+      <c r="D31" s="26"/>
+      <c r="E31" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="27"/>
-      <c r="G31" s="25" t="s">
+      <c r="F31" s="26"/>
+      <c r="G31" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="H31" s="27"/>
-      <c r="I31" s="25" t="s">
+      <c r="H31" s="26"/>
+      <c r="I31" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="J31" s="26"/>
-      <c r="K31" s="27"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="26"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -2470,10 +2480,10 @@
       <c r="Y31" s="1"/>
     </row>
     <row r="32" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23">
+      <c r="A32" s="32">
         <v>12</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="22" t="s">
         <v>63</v>
       </c>
       <c r="C32" s="11" t="s">
@@ -2491,11 +2501,11 @@
       <c r="G32" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H32" s="29" t="s">
+      <c r="H32" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I32" s="26"/>
-      <c r="J32" s="27"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="26"/>
       <c r="K32" s="18" t="s">
         <v>27</v>
       </c>
@@ -2515,8 +2525,8 @@
       <c r="Y32" s="1"/>
     </row>
     <row r="33" spans="1:25" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="22"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="23"/>
       <c r="C33" s="8" t="s">
         <v>70</v>
       </c>
@@ -2532,11 +2542,11 @@
       <c r="G33" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H33" s="25" t="s">
+      <c r="H33" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="I33" s="26"/>
-      <c r="J33" s="30"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="56"/>
       <c r="K33" s="19" t="s">
         <v>76</v>
       </c>
@@ -2556,25 +2566,25 @@
       <c r="Y33" s="1"/>
     </row>
     <row r="34" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23">
+      <c r="A34" s="32">
         <v>13</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="35" t="s">
+      <c r="C34" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="35" t="s">
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="47"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="34"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -2591,21 +2601,21 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" spans="1:25" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="49" t="s">
+      <c r="A35" s="33"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="27"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="26"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -2622,10 +2632,10 @@
       <c r="Y35" s="1"/>
     </row>
     <row r="36" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23">
+      <c r="A36" s="32">
         <v>14</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="22" t="s">
         <v>80</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -2634,19 +2644,19 @@
       <c r="D36" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="35" t="s">
+      <c r="E36" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="50" t="s">
+      <c r="F36" s="26"/>
+      <c r="G36" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="H36" s="51"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="50" t="s">
+      <c r="H36" s="37"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="K36" s="52"/>
+      <c r="K36" s="38"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -2663,27 +2673,27 @@
       <c r="Y36" s="1"/>
     </row>
     <row r="37" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="22"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="23"/>
       <c r="C37" s="20" t="s">
         <v>86</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E37" s="53" t="s">
+      <c r="E37" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="F37" s="54"/>
-      <c r="G37" s="25" t="s">
+      <c r="F37" s="30"/>
+      <c r="G37" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="H37" s="26"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="53" t="s">
+      <c r="H37" s="25"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="K37" s="55"/>
+      <c r="K37" s="31"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -2700,25 +2710,25 @@
       <c r="Y37" s="1"/>
     </row>
     <row r="38" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="23">
+      <c r="A38" s="32">
         <v>15</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="45" t="s">
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="47"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="34"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -2735,8 +2745,8 @@
       <c r="Y38" s="1"/>
     </row>
     <row r="39" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="22"/>
+      <c r="A39" s="55"/>
+      <c r="B39" s="23"/>
       <c r="C39" s="17" t="s">
         <v>94</v>
       </c>
@@ -2766,10 +2776,10 @@
       <c r="Y39" s="1"/>
     </row>
     <row r="40" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="23">
+      <c r="A40" s="32">
         <v>16</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="22" t="s">
         <v>96</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -2784,15 +2794,15 @@
       <c r="F40" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G40" s="35" t="s">
+      <c r="G40" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="H40" s="27"/>
-      <c r="I40" s="35" t="s">
+      <c r="H40" s="26"/>
+      <c r="I40" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J40" s="26"/>
-      <c r="K40" s="27"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="26"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
@@ -2809,8 +2819,8 @@
       <c r="Y40" s="1"/>
     </row>
     <row r="41" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="22"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="23"/>
       <c r="C41" s="14" t="s">
         <v>102</v>
       </c>
@@ -2820,18 +2830,18 @@
       <c r="E41" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="F41" s="56" t="s">
+      <c r="F41" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G41" s="48" t="s">
+      <c r="G41" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="H41" s="27"/>
-      <c r="I41" s="48" t="s">
+      <c r="H41" s="26"/>
+      <c r="I41" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="J41" s="26"/>
-      <c r="K41" s="27"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="26"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
@@ -2854,17 +2864,17 @@
       <c r="B42" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="27"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="26"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
@@ -2881,29 +2891,29 @@
       <c r="Y42" s="1"/>
     </row>
     <row r="43" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23">
+      <c r="A43" s="32">
         <v>18</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C43" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="27"/>
-      <c r="E43" s="35" t="s">
+      <c r="D43" s="26"/>
+      <c r="E43" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="F43" s="27"/>
-      <c r="G43" s="35" t="s">
+      <c r="F43" s="26"/>
+      <c r="G43" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="H43" s="27"/>
-      <c r="I43" s="35" t="s">
+      <c r="H43" s="26"/>
+      <c r="I43" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="J43" s="26"/>
-      <c r="K43" s="27"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="26"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
@@ -2920,25 +2930,25 @@
       <c r="Y43" s="1"/>
     </row>
     <row r="44" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="25" t="s">
+      <c r="A44" s="55"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="27"/>
-      <c r="E44" s="25" t="s">
+      <c r="D44" s="26"/>
+      <c r="E44" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="F44" s="27"/>
-      <c r="G44" s="25" t="s">
+      <c r="F44" s="26"/>
+      <c r="G44" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="H44" s="27"/>
-      <c r="I44" s="25" t="s">
+      <c r="H44" s="26"/>
+      <c r="I44" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="J44" s="26"/>
-      <c r="K44" s="27"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="26"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
@@ -2955,10 +2965,10 @@
       <c r="Y44" s="1"/>
     </row>
     <row r="45" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="23">
+      <c r="A45" s="32">
         <v>19</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="22" t="s">
         <v>119</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -3004,8 +3014,8 @@
       <c r="Y45" s="1"/>
     </row>
     <row r="46" spans="1:25" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="28"/>
-      <c r="B46" s="22"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="23"/>
       <c r="C46" s="8" t="s">
         <v>128</v>
       </c>
@@ -3031,7 +3041,7 @@
         <v>44</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -3106,7 +3116,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
+      <c r="D49" s="57"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -28565,25 +28575,60 @@
     </row>
   </sheetData>
   <mergeCells count="102">
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C21:K21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A7:K9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:K43"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="A40:A41"/>
@@ -28608,65 +28653,30 @@
     <mergeCell ref="I44:K44"/>
     <mergeCell ref="E44:F44"/>
     <mergeCell ref="G44:H44"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A7:K9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="J37:K37"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G16:K16"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="G19:K19"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="C21:K21"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
